--- a/resource/groundTruths/decision/CF_M05_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M05_ground_truth_decision.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43AC6C71-91BD-7648-BA25-7BB2DE29ECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDEF6C6-3FEF-BF46-BECA-EC6A50CB73F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="1240" windowWidth="27900" windowHeight="16460" xr2:uid="{B46AF004-DAD2-1D43-B453-FF5003BCD68B}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="14480" windowHeight="16560" xr2:uid="{B46AF004-DAD2-1D43-B453-FF5003BCD68B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
   <si>
     <t>Document ID</t>
   </si>
@@ -97,167 +97,143 @@
     <t>CF_M05</t>
   </si>
   <si>
-    <t>CF_M05_AD1</t>
-  </si>
-  <si>
     <t>CF_M05_P01</t>
   </si>
   <si>
-    <t>CF_M05_C07 *</t>
-  </si>
-  <si>
-    <t>flexibility and scalability (Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application. )</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>CF_M05_AD2</t>
-  </si>
-  <si>
     <t>CF_M05_AU01</t>
   </si>
   <si>
-    <t>CF_M05_C09 *</t>
-  </si>
-  <si>
-    <t>integrity and confidentiality (In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.)</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>CF_M05_AD3</t>
-  </si>
-  <si>
     <t>CF_M05_AU02</t>
   </si>
   <si>
-    <t>CF_M05_C01 *</t>
-  </si>
-  <si>
-    <t>visual and functional coherence (the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.)</t>
-  </si>
-  <si>
-    <t>CF_M05_AD4</t>
-  </si>
-  <si>
     <t>CF_M05_AU03</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>confidentiality (This microservice is essential for maintaining data confidentiality and protection.)</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>CF_M05_AD5</t>
-  </si>
-  <si>
     <t>CF_M05_AU04</t>
   </si>
   <si>
     <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
   </si>
   <si>
-    <t>CF_M05_AD6</t>
-  </si>
-  <si>
-    <t>CF_M05_P02</t>
-  </si>
-  <si>
-    <t>CF_M05_C06, CF_M05_C07, CF_M05_C08 *</t>
-  </si>
-  <si>
-    <t>scalability, availability, accessibility and maintainability (The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.)</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>CF_M05_AD7</t>
-  </si>
-  <si>
-    <t>CF_M05_P03, CF_M05_AU22</t>
-  </si>
-  <si>
-    <t>presentation and user experience (This separation of responsibilities allows the client to focus on presentation and user experience.)</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>CF_M05_AD8</t>
-  </si>
-  <si>
-    <t>CF_M05_P03, CF_M05_AU23</t>
-  </si>
-  <si>
-    <t>security, data integrity, persistence (This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.)</t>
-  </si>
-  <si>
-    <t>CF_M05_AD9</t>
-  </si>
-  <si>
-    <t>CF_M05_AU17</t>
-  </si>
-  <si>
     <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
   </si>
   <si>
-    <t>76</t>
+    <t>CF_M05_AD11</t>
+  </si>
+  <si>
+    <t>CF_M05_C06, CF_M05_C07</t>
+  </si>
+  <si>
+    <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+  </si>
+  <si>
+    <t>CF_M05_P05</t>
+  </si>
+  <si>
+    <t>CF_M05_P02, CF_M05_AU06</t>
+  </si>
+  <si>
+    <t>CF_M05_P02, CF_M05_AU32</t>
+  </si>
+  <si>
+    <t>CF_M05_AU30</t>
+  </si>
+  <si>
+    <t>CF_M05_AU30, CF_M05_AU29</t>
+  </si>
+  <si>
+    <t>CF_M05_AU07</t>
+  </si>
+  <si>
+    <t>CF_M05_AD01</t>
+  </si>
+  <si>
+    <t>CF_M05_AD02</t>
+  </si>
+  <si>
+    <t>CF_M05_AD03</t>
+  </si>
+  <si>
+    <t>CF_M05_AD04</t>
+  </si>
+  <si>
+    <t>CF_M05_AD05</t>
+  </si>
+  <si>
+    <t>CF_M05_AD06</t>
+  </si>
+  <si>
+    <t>CF_M05_AD07</t>
+  </si>
+  <si>
+    <t>CF_M05_AD08</t>
+  </si>
+  <si>
+    <t>CF_M05_AD09</t>
   </si>
   <si>
     <t>CF_M05_AD10</t>
   </si>
   <si>
-    <t>Spring Data &amp; JPA 2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> This combination is used to manage data persistence, which allows you to interact with databases in a simpler, object-oriented way.</t>
-  </si>
-  <si>
-    <t>CF_M05_AD11</t>
-  </si>
-  <si>
-    <t>CF_M05_AU17, CF_M05_AU18, CF_M05_AU19</t>
-  </si>
-  <si>
-    <t>maintainability (When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.)</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>CF_M05_AD12</t>
-  </si>
-  <si>
-    <t>CF_M05_AU25</t>
-  </si>
-  <si>
-    <t>CF_M05_C06, CF_M05_C07</t>
-  </si>
-  <si>
-    <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>CF_M05_AD13</t>
-  </si>
-  <si>
-    <t>CF_M05_AD14</t>
+    <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
+  </si>
+  <si>
+    <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
+  </si>
+  <si>
+    <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+  </si>
+  <si>
+    <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+  </si>
+  <si>
+    <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+  </si>
+  <si>
+    <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+  </si>
+  <si>
+    <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+  </si>
+  <si>
+    <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+  </si>
+  <si>
+    <t>CF_M05_C07 , CF_M05_C10, CF_M05_C18</t>
+  </si>
+  <si>
+    <t>CF_M05_C09 , CF_M05_C11</t>
+  </si>
+  <si>
+    <t>CF_M05_C01, CF_M05_C12</t>
+  </si>
+  <si>
+    <t>CF_M05_C11</t>
+  </si>
+  <si>
+    <t>CF_M05_C13</t>
+  </si>
+  <si>
+    <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, CF_M05_C18</t>
+  </si>
+  <si>
+    <t>CF_M05_C15</t>
+  </si>
+  <si>
+    <t>CF_M05_C09 , CF_M05_C16, CF_M05_C17</t>
+  </si>
+  <si>
+    <t>CF_M05_C07, CF_M05_C14, CF_M05_C18</t>
+  </si>
+  <si>
+    <t>CF_M05_C14</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -275,18 +251,27 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -299,8 +284,14 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -308,33 +299,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -344,14 +314,40 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -395,10 +391,10 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Architectural Decisions-style" pivot="0" count="4" xr9:uid="{FDB957AD-61A7-B143-96EE-974410A8AF73}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -413,7 +409,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC2501B0-11D1-2B4C-AF26-56FB1CA3963F}" name="Taula4_2" displayName="Taula4_2" ref="A1:F15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC2501B0-11D1-2B4C-AF26-56FB1CA3963F}" name="Taula4_2" displayName="Taula4_2" ref="A1:F12" headerRowDxfId="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{410706A8-41AC-524F-B7F4-0C19D49A9604}" name="Document ID"/>
     <tableColumn id="2" xr3:uid="{562273DB-27D6-5747-877C-6CD5805C31A6}" name="AD ID"/>
@@ -723,294 +719,252 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C6B1BB-1BBF-8749-A7B3-8928D92012D1}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="7">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="D4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="7">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="7">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="D6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F6" s="7">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="7">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="7">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F10" s="7">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="F12" s="7">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:F15" xr:uid="{5DC3613F-4248-CC4B-A5B6-C0631EF8DFF7}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:F12" xr:uid="{5DC3613F-4248-CC4B-A5B6-C0631EF8DFF7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/resource/groundTruths/decision/CF_M05_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M05_ground_truth_decision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDEF6C6-3FEF-BF46-BECA-EC6A50CB73F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10574866-674C-1244-8D1B-1E01B6669DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="14480" windowHeight="16560" xr2:uid="{B46AF004-DAD2-1D43-B453-FF5003BCD68B}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17080" xr2:uid="{B46AF004-DAD2-1D43-B453-FF5003BCD68B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,6 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve"> [Threaded comment] Your version of Excel allows you to read this threaded comment; however, any edits to it will be removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924 Comment: concept, requirement</t>
         </r>
@@ -74,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
   <si>
     <t>Document ID</t>
   </si>
@@ -130,12 +129,6 @@
     <t>CF_M05_P05</t>
   </si>
   <si>
-    <t>CF_M05_P02, CF_M05_AU06</t>
-  </si>
-  <si>
-    <t>CF_M05_P02, CF_M05_AU32</t>
-  </si>
-  <si>
     <t>CF_M05_AU30</t>
   </si>
   <si>
@@ -199,41 +192,44 @@
     <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
   </si>
   <si>
-    <t>CF_M05_C07 , CF_M05_C10, CF_M05_C18</t>
-  </si>
-  <si>
-    <t>CF_M05_C09 , CF_M05_C11</t>
-  </si>
-  <si>
-    <t>CF_M05_C01, CF_M05_C12</t>
-  </si>
-  <si>
-    <t>CF_M05_C11</t>
-  </si>
-  <si>
-    <t>CF_M05_C13</t>
-  </si>
-  <si>
-    <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, CF_M05_C18</t>
-  </si>
-  <si>
-    <t>CF_M05_C15</t>
-  </si>
-  <si>
-    <t>CF_M05_C09 , CF_M05_C16, CF_M05_C17</t>
-  </si>
-  <si>
-    <t>CF_M05_C07, CF_M05_C14, CF_M05_C18</t>
-  </si>
-  <si>
-    <t>CF_M05_C14</t>
+    <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
+  </si>
+  <si>
+    <t>CF_M05_C09 , *CF_M05_C11</t>
+  </si>
+  <si>
+    <t>CF_M05_C01, *CF_M05_C12</t>
+  </si>
+  <si>
+    <t>*CF_M05_C11</t>
+  </si>
+  <si>
+    <t>*CF_M05_C13</t>
+  </si>
+  <si>
+    <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
+  </si>
+  <si>
+    <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+  </si>
+  <si>
+    <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+  </si>
+  <si>
+    <t>*CF_M05_C14</t>
+  </si>
+  <si>
+    <t>CF_M05_P02</t>
+  </si>
+  <si>
+    <t>*CF_M05_C15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -270,6 +266,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -303,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -321,9 +323,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -747,18 +746,18 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="7">
+        <v>31</v>
+      </c>
+      <c r="F2" s="1">
         <v>56</v>
       </c>
     </row>
@@ -767,18 +766,18 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="7">
+        <v>32</v>
+      </c>
+      <c r="F3" s="1">
         <v>57</v>
       </c>
     </row>
@@ -787,18 +786,18 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="7">
+        <v>33</v>
+      </c>
+      <c r="F4" s="1">
         <v>57</v>
       </c>
     </row>
@@ -807,18 +806,18 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="7">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1">
         <v>58</v>
       </c>
     </row>
@@ -827,18 +826,18 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="1">
         <v>58</v>
       </c>
     </row>
@@ -847,18 +846,18 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="7">
+        <v>35</v>
+      </c>
+      <c r="F7" s="1">
         <v>60</v>
       </c>
     </row>
@@ -867,18 +866,18 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="7">
+        <v>36</v>
+      </c>
+      <c r="F8" s="1">
         <v>61</v>
       </c>
     </row>
@@ -887,18 +886,18 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="7">
+        <v>37</v>
+      </c>
+      <c r="F9" s="1">
         <v>61</v>
       </c>
     </row>
@@ -907,18 +906,18 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="1">
         <v>76</v>
       </c>
     </row>
@@ -927,18 +926,18 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="7">
+        <v>38</v>
+      </c>
+      <c r="F11" s="1">
         <v>77</v>
       </c>
     </row>
@@ -950,7 +949,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>15</v>
@@ -958,7 +957,7 @@
       <c r="E12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="1">
         <v>81</v>
       </c>
     </row>

--- a/resource/groundTruths/decision/CF_M05_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M05_ground_truth_decision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10574866-674C-1244-8D1B-1E01B6669DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DBD150-296C-9C49-8F92-F14A806906C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17080" xr2:uid="{B46AF004-DAD2-1D43-B453-FF5003BCD68B}"/>
+    <workbookView xWindow="11160" yWindow="740" windowWidth="18240" windowHeight="17080" xr2:uid="{B46AF004-DAD2-1D43-B453-FF5003BCD68B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
   <si>
     <t>Document ID</t>
   </si>
@@ -223,6 +223,24 @@
   </si>
   <si>
     <t>*CF_M05_C15</t>
+  </si>
+  <si>
+    <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+  </si>
+  <si>
+    <t>CF_M05_AD12</t>
+  </si>
+  <si>
+    <t>CF_M05_AU29</t>
+  </si>
+  <si>
+    <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
+  </si>
+  <si>
+    <t>CF_M05_AD13</t>
+  </si>
+  <si>
+    <t>*CF_M05_C18</t>
   </si>
 </sst>
 </file>
@@ -293,7 +311,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -301,11 +319,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF356854"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF356854"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF356854"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF356854"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -323,6 +381,20 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C6B1BB-1BBF-8749-A7B3-8928D92012D1}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.2">
@@ -959,6 +1031,46 @@
       </c>
       <c r="F12" s="1">
         <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="9">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="12">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
